--- a/data/S2009_10_FINAL.xlsx
+++ b/data/S2009_10_FINAL.xlsx
@@ -27,8 +27,11 @@
     <sheet name="SERIES" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="CLUBS" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="META" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$12</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -36,7 +39,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,8 +54,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -69,6 +76,11 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -82,11 +94,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -10431,7 +10449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10512,6 +10530,153 @@
       <c r="E3" t="inlineStr">
         <is>
           <t>CLUB_S2009_10_0185</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S2009_10_0031 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S2009_10_0032 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S2009_10_0033 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S2009_10_0138 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S2009_10_0139 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S2009_10_0140 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S2009_10_0141 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S2009_10_0142 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0021</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S2009_10_0021 'Baráž o Extraligu' (L15, parent=NODE_S2009_10_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0028</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S2009_10_0028 'Baráž o I.ligu' (L25, parent=NODE_S2009_10_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0041</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S2009_10_0041 'O postup do I.ligy' (L25, parent=NODE_S2009_10_0035) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -13868,8 +14033,6 @@
         </is>
       </c>
     </row>
-    <row r="79"/>
-    <row r="80"/>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
@@ -13949,7 +14112,6 @@
         </is>
       </c>
     </row>
-    <row r="88"/>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
@@ -27343,6 +27505,303 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0031</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0031 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0032</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0032 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0033</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0033 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0138</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0138 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0139</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0139 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0140</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0140 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0141</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0141 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0142</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0142 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0021</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S2009_10_0021 'Baráž o Extraligu' (L15, parent=NODE_S2009_10_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0028</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S2009_10_0028 'Baráž o I.ligu' (L25, parent=NODE_S2009_10_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0041</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S2009_10_0041 'O postup do I.ligy' (L25, parent=NODE_S2009_10_0035) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F12"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S2009_10_FINAL.xlsx
+++ b/data/S2009_10_FINAL.xlsx
@@ -30,7 +30,7 @@
     <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -10449,7 +10449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10536,7 +10536,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S2009_10_0031 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -10548,7 +10548,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S2009_10_0032 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -10560,7 +10560,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S2009_10_0033 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -10572,7 +10572,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S2009_10_0138 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -10584,7 +10584,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S2009_10_0139 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -10596,7 +10596,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S2009_10_0140 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -10608,7 +10608,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S2009_10_0141 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hockey Club Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -10620,7 +10620,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S2009_10_0142 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -10630,14 +10630,9 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>NODE_S2009_10_0021</t>
-        </is>
-      </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S2009_10_0021 'Baráž o Extraligu' (L15, parent=NODE_S2009_10_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -10647,14 +10642,9 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>NODE_S2009_10_0028</t>
-        </is>
-      </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S2009_10_0028 'Baráž o I.ligu' (L25, parent=NODE_S2009_10_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SHC Maso Brejcha Klatovy' → 'Klatovy' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -10664,17 +10654,298 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>NODE_S2009_10_0041</t>
-        </is>
-      </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S2009_10_0041 'O postup do I.ligy' (L25, parent=NODE_S2009_10_0035) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Predators Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'SC Kolín' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Valašský hokejový klub Vsetín' → 'Vsetín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0030</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  Skupina A'</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0031</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  Skupina B'</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -14033,6 +14304,8 @@
         </is>
       </c>
     </row>
+    <row r="79"/>
+    <row r="80"/>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
@@ -14063,6 +14336,11 @@
           <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0001</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -14075,6 +14353,11 @@
           <t>Kvalifikace o II.ligu</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0003</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -14087,6 +14370,11 @@
           <t>Krajské přebory (nové velké kraje!)</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0003</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -14099,6 +14387,11 @@
           <t>I.třída / I.B třída / Krajská soutěž</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0035</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -14112,6 +14405,7 @@
         </is>
       </c>
     </row>
+    <row r="88"/>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
@@ -17823,12 +18117,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec.</t>
+          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec. || TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>TŽ VŘSR Třinec</t>
+          <t>Třinec</t>
         </is>
       </c>
     </row>
@@ -17949,12 +18243,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -18122,12 +18416,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -18248,12 +18542,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Chomutov = KLH VT VTJ Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **KLH VT VTJ** = post-revolucni nazev (KLH = klub lední hokej, VT = vrcholový tým, VTJ = Vojenská tělovýchovná jednota). city Chomutov.</t>
+          <t>Chomutov = KLH VT VTJ Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **KLH VT VTJ** = post-revolucni nazev (KLH = klub lední hokej, VT = vrcholový tým, VTJ = Vojenská tělovýchovná jednota). city Chomutov. || TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>KLH VT VTJ Chomutov</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -18332,12 +18626,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -18500,12 +18794,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Kadaň = Sportovní klub Kadaň (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj (okres Chomutov). city Kadaň.</t>
+          <t>Kadaň = Sportovní klub Kadaň (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj (okres Chomutov). city Kadaň. || TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Sportovní klub Kadaň</t>
+          <t>Kadaň</t>
         </is>
       </c>
     </row>
@@ -18547,12 +18841,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>L20 entita ukončena, klub pokračoval přes B tým (HC Tábor B -FeKS, CLUB_S2009_10_0114), který se stal hlavní entitou od 10/11. || Tábor = Hockey Club Tábor (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj. city Tábor.</t>
+          <t>L20 entita ukončena, klub pokračoval přes B tým (HC Tábor B -FeKS, CLUB_S2009_10_0114), který se stal hlavní entitou od 10/11. || Tábor = Hockey Club Tábor (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj. city Tábor. || TBD: city 'Hockey Club Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Hockey Club Tábor</t>
+          <t>Tábor</t>
         </is>
       </c>
     </row>
@@ -19046,12 +19340,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Slaný = UHK LEV Slaný (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kladno). **UHK** = Univerzitni hokejovy klub. Patterns: HK Lev Slaný. city Slaný.</t>
+          <t>Slaný = UHK LEV Slaný (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kladno). **UHK** = Univerzitni hokejovy klub. Patterns: HK Lev Slaný. city Slaný. || TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>UHK LEV Slaný</t>
+          <t>Slaný</t>
         </is>
       </c>
     </row>
@@ -19715,12 +20009,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří.</t>
+          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří. || TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Klášterec</t>
+          <t>Klášterec nad Ohří</t>
         </is>
       </c>
     </row>
@@ -19794,12 +20088,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Klatovy = SHC Maso Brejcha Klatovy (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. **Maso Brejcha** = sponzor (řeznictví). city Klatovy.</t>
+          <t>Klatovy = SHC Maso Brejcha Klatovy (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. **Maso Brejcha** = sponzor (řeznictví). city Klatovy. || TBD: city 'SHC Maso Brejcha Klatovy' → 'Klatovy' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>SHC Maso Brejcha Klatovy</t>
+          <t>Klatovy</t>
         </is>
       </c>
     </row>
@@ -19925,12 +20219,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Jablonec nad Nisou = HC Vlci Jablonec nL Nisou (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. city Jablonec nad Nisou.</t>
+          <t>Jablonec nad Nisou = HC Vlci Jablonec nL Nisou (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. city Jablonec nad Nisou. || TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Vlci Jablonec nad Nisou</t>
+          <t>Jablonec nad Nisou</t>
         </is>
       </c>
     </row>
@@ -19972,12 +20266,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Česká Lípa = HC Predators Česká Lípa (Wiki D42 - registr ustavy 04/2026). Liberecky kraj. Post-revolucni anglicky nazev. city Česká Lípa.</t>
+          <t>Česká Lípa = HC Predators Česká Lípa (Wiki D42 - registr ustavy 04/2026). Liberecky kraj. Post-revolucni anglicky nazev. city Česká Lípa. || TBD: city 'Predators Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Predators Česká Lípa</t>
+          <t>Česká Lípa</t>
         </is>
       </c>
     </row>
@@ -20056,12 +20350,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -20140,12 +20434,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'SC Kolín' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>SC Kolín</t>
         </is>
       </c>
     </row>
@@ -20313,12 +20607,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Nymburk = NED Hockey Nymburk (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. Post-revolucni. city Nymburk.</t>
+          <t>Nymburk = NED Hockey Nymburk (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. Post-revolucni. city Nymburk. || TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>NED Hockey Nymburk</t>
+          <t>Nymburk</t>
         </is>
       </c>
     </row>
@@ -20607,12 +20901,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Vsetín = Valašský hokejový klub Vsetín (Wiki D42 - registr ustavy 04/2026). Zlinsky kraj. **VHK** = Valašský hokejový klub. city Vsetín.</t>
+          <t>Vsetín = Valašský hokejový klub Vsetín (Wiki D42 - registr ustavy 04/2026). Zlinsky kraj. **VHK** = Valašský hokejový klub. city Vsetín. || TBD: city 'Valašský hokejový klub Vsetín' → 'Vsetín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Valašský hokejový klub Vsetín</t>
+          <t>Vsetín</t>
         </is>
       </c>
     </row>
@@ -20817,12 +21111,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Brno = VSK Technika Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VSK Technika** = Vysokoškolský sportovní klub (VUT Brno). city Brno.</t>
+          <t>Brno = VSK Technika Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VSK Technika** = Vysokoškolský sportovní klub (VUT Brno). city Brno. || TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>VSK Technika Brno</t>
+          <t>Technika Brno</t>
         </is>
       </c>
     </row>
@@ -20948,12 +21242,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Slaný = UHK LEV Slaný (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kladno). **UHK** = Univerzitni hokejovy klub. Patterns: HK Lev Slaný. city Slaný.</t>
+          <t>Slaný = UHK LEV Slaný (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kladno). **UHK** = Univerzitni hokejovy klub. Patterns: HK Lev Slaný. city Slaný. || TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>UHK LEV Slaný</t>
+          <t>Slaný</t>
         </is>
       </c>
     </row>
@@ -20990,12 +21284,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -21966,12 +22260,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Lokomotiva  Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -22302,12 +22596,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -22559,12 +22853,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Plzeň = HC Ekonomické Stavby Plzeň (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. city Plzeň.</t>
+          <t>Plzeň = HC Ekonomické Stavby Plzeň (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. city Plzeň. || TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Ekonomické Stavby Plzeň</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -23315,12 +23609,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Nová Paka = BK JTC Nová Paka (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Jicin). **BK JTC** = Bruslarsky klub Jicinske telovychovne centrum. city Nová Paka.</t>
+          <t>Nová Paka = BK JTC Nová Paka (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Jicin). **BK JTC** = Bruslarsky klub Jicinske telovychovne centrum. city Nová Paka. || TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>BK JTC Nová Paka</t>
+          <t>Nová Paka</t>
         </is>
       </c>
     </row>
@@ -23525,12 +23819,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Nový Bydžov = TJ Stadion Nový Bydžov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj. Patterns: OSP Nový Bydžov. city Nový Bydžov.</t>
+          <t>Nový Bydžov = TJ Stadion Nový Bydžov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj. Patterns: OSP Nový Bydžov. city Nový Bydžov. || TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Stadion Nový Bydžov</t>
+          <t>Nový Bydžov</t>
         </is>
       </c>
     </row>
@@ -23646,12 +23940,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Světlá nad Sázavou = HC SB Světlá nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj (okres Havlickuv Brod). '(VYS)' = Vysocina. **SB** = pravdepodobne stavebni podnik. city Světlá nad Sázavou.</t>
+          <t>Světlá nad Sázavou = HC SB Světlá nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj (okres Havlickuv Brod). '(VYS)' = Vysocina. **SB** = pravdepodobne stavebni podnik. city Světlá nad Sázavou. || TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>SB Světlá nad Sázavou</t>
+          <t>Světlá nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -24197,12 +24491,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>Moravské Budějovice</t>
         </is>
       </c>
     </row>
@@ -24795,12 +25089,12 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod.</t>
+          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod. || TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>Havlíčkův Brod</t>
+          <t>Rožnov pod Radhoštěm</t>
         </is>
       </c>
     </row>
@@ -27511,11 +27805,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -27560,21 +27854,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S2009_10_0031</t>
+          <t>CLUB_S2009_10_0006</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>CLUB_S2009_10_0031 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -27582,21 +27874,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S2009_10_0032</t>
+          <t>CLUB_S2009_10_0009</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>CLUB_S2009_10_0032 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -27604,21 +27894,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S2009_10_0033</t>
+          <t>CLUB_S2009_10_0013</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>CLUB_S2009_10_0033 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -27626,21 +27914,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S2009_10_0138</t>
+          <t>CLUB_S2009_10_0016</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>CLUB_S2009_10_0138 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -27648,21 +27934,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S2009_10_0139</t>
+          <t>CLUB_S2009_10_0018</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>CLUB_S2009_10_0139 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -27670,21 +27954,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S2009_10_0140</t>
+          <t>CLUB_S2009_10_0022</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>CLUB_S2009_10_0140 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+          <t>TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -27692,21 +27974,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S2009_10_0141</t>
+          <t>CLUB_S2009_10_0023</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>CLUB_S2009_10_0141 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+          <t>TBD: city 'Hockey Club Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -27714,21 +27994,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S2009_10_0142</t>
+          <t>CLUB_S2009_10_0036</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>CLUB_S2009_10_0142 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+          <t>TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -27736,21 +28014,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NODE_S2009_10_0021</t>
+          <t>CLUB_S2009_10_0054</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S2009_10_0021 'Baráž o Extraligu' (L15, parent=NODE_S2009_10_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -27758,21 +28034,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NODE_S2009_10_0028</t>
+          <t>CLUB_S2009_10_0057</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S2009_10_0028 'Baráž o I.ligu' (L25, parent=NODE_S2009_10_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+          <t>TBD: city 'SHC Maso Brejcha Klatovy' → 'Klatovy' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -27780,24 +28054,482 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NODE_S2009_10_0041</t>
+          <t>CLUB_S2009_10_0060</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S2009_10_0041 'O postup do I.ligy' (L25, parent=NODE_S2009_10_0035) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+          <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0061</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Predators Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0064</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0066</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Chomutov' → 'SC Kolín' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0070</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0078</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Valašský hokejový klub Vsetín' → 'Vsetín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0083</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0086</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0087</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0110</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0110</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0118</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0124</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0133</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0147</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0148</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0153</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0160</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0161</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0170</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0175</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0192</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0030</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  Skupina A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0031</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  Skupina B'</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F12"/>
+  <autoFilter ref="A1:F35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S2009_10_FINAL.xlsx
+++ b/data/S2009_10_FINAL.xlsx
@@ -30,7 +30,7 @@
     <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -10449,7 +10449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10548,7 +10548,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -10560,7 +10560,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -10572,7 +10572,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hockey Club Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -10584,7 +10584,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -10596,7 +10596,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -10608,7 +10608,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hockey Club Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SHC Maso Brejcha Klatovy' → 'Klatovy' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -10620,7 +10620,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -10632,7 +10632,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Predators Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -10644,7 +10644,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SHC Maso Brejcha Klatovy' → 'Klatovy' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -10656,7 +10656,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -10668,7 +10668,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Predators Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Valašský hokejový klub Vsetín' → 'Vsetín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -10680,7 +10680,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -10692,7 +10692,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'SC Kolín' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -10704,7 +10704,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -10716,7 +10716,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Valašský hokejový klub Vsetín' → 'Vsetín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -10728,7 +10728,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -10740,7 +10740,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -10752,7 +10752,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -10764,7 +10764,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -10776,7 +10776,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -10788,7 +10788,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -10800,7 +10800,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -10810,9 +10810,14 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0030</t>
+        </is>
+      </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  Skupina A'</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -10822,130 +10827,17 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0031</t>
+        </is>
+      </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  Skupina B'</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>NODE_S2009_10_0030</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  Skupina A'</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>NODE_S2009_10_0031</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  Skupina B'</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -11020,7 +10912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K92"/>
+  <dimension ref="A1:L92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11079,6 +10971,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11121,6 +11018,11 @@
           <t>14 týmů (5 stat sloupců): základ + QF/SF/finále + baráž. Mistr: HC Eaton Pardubice.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11168,6 +11070,11 @@
           <t>Vítězové 4 skupin II.ligy. Dvoukolově. Top 2 do I.ligy.</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11210,6 +11117,11 @@
           <t>I.ČNHL: základ + playoff (QF/SF/finále/O 3.) + O 5.-8. + o udržení. I.SNHL (12). Kval o I.ligu.</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11252,6 +11164,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11294,6 +11211,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11336,6 +11258,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11378,6 +11305,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11420,6 +11352,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11462,6 +11399,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -11504,6 +11446,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0010</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -11546,6 +11493,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -11588,6 +11540,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0012</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -11630,6 +11587,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0013</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -11672,6 +11634,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0014</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -11714,6 +11681,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0015</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -11756,6 +11728,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0016</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -11798,6 +11775,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0017</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -11840,6 +11822,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0018</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -11882,6 +11869,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0019</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -11924,6 +11916,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0020</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -11966,6 +11963,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0021</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -12008,6 +12010,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0022</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -12050,6 +12057,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0023</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -12092,6 +12104,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0024</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -12134,6 +12151,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -12176,6 +12198,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0026</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -12218,6 +12245,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0027</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -12260,6 +12292,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0028</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -12307,6 +12344,11 @@
           <t>Kvalifikace o postup do II.ligy</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0029</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -12339,6 +12381,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0030</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -12371,6 +12418,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0031</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -12413,6 +12465,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0033</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -12539,6 +12596,11 @@
           <t>II.liga: 2 skupiny + finále + o postup do I.ligy.</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0036</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -12581,6 +12643,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0037</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -12623,6 +12690,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0038</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -12665,6 +12737,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0039</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -12707,6 +12784,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0040</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -12749,6 +12831,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0041</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -12791,6 +12878,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0042</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -12833,6 +12925,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0043</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -12875,6 +12972,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0044</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -12917,6 +13019,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0045</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -12959,6 +13066,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0046</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -13001,6 +13113,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0047</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -13043,6 +13160,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0048</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -13085,6 +13207,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0049</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -13127,6 +13254,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0050</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -13169,6 +13301,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0051</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -13211,6 +13348,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0052</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -13253,6 +13395,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0053</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -13295,6 +13442,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0054</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -13421,6 +13573,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0055</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -13463,6 +13620,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0057</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -13505,6 +13667,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0058</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -13547,6 +13714,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0059</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -13589,6 +13761,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0060</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -13631,6 +13808,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0061</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -13673,6 +13855,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0062</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -13715,6 +13902,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0063</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -13799,6 +13991,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0064</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -13841,6 +14038,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0065</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -13967,6 +14169,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0065</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -14051,6 +14258,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0071</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -14093,6 +14305,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0073</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -14217,6 +14434,11 @@
       <c r="K76" t="inlineStr">
         <is>
           <t>Kontejner L40</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0076</t>
         </is>
       </c>
     </row>
@@ -14324,6 +14546,11 @@
           <t>I.liga (10 týmů, jeden stůl)</t>
         </is>
       </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>L10</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -14341,6 +14568,11 @@
           <t>NODE_S2009_10_0001</t>
         </is>
       </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -14358,6 +14590,11 @@
           <t>NODE_S2009_10_0003</t>
         </is>
       </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>L25</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -14375,6 +14612,11 @@
           <t>NODE_S2009_10_0003</t>
         </is>
       </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>L30</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -14392,6 +14634,11 @@
           <t>NODE_S2009_10_0035</t>
         </is>
       </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -14402,6 +14649,11 @@
       <c r="B87" t="inlineStr">
         <is>
           <t>Okresní přebory (jen registr)</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>okresní</t>
         </is>
       </c>
     </row>
@@ -18243,12 +18495,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -18416,12 +18668,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -18626,12 +18878,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -20434,12 +20686,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'SC Kolín' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>SC Kolín</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -21284,12 +21536,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -22260,12 +22512,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Veselí nad Lužnicí</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -22596,12 +22848,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -24491,12 +24743,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Moravské Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -25089,12 +25341,12 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod. || TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod.</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>Rožnov pod Radhoštěm</t>
+          <t>Havlíčkův Brod</t>
         </is>
       </c>
     </row>
@@ -27805,7 +28057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -27879,12 +28131,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S2009_10_0009</t>
+          <t>CLUB_S2009_10_0016</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -27899,12 +28151,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S2009_10_0013</t>
+          <t>CLUB_S2009_10_0022</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -27919,12 +28171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S2009_10_0016</t>
+          <t>CLUB_S2009_10_0023</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Hockey Club Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -27939,12 +28191,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S2009_10_0018</t>
+          <t>CLUB_S2009_10_0036</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -27959,12 +28211,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S2009_10_0022</t>
+          <t>CLUB_S2009_10_0054</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -27979,12 +28231,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S2009_10_0023</t>
+          <t>CLUB_S2009_10_0057</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Hockey Club Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'SHC Maso Brejcha Klatovy' → 'Klatovy' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -27999,12 +28251,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S2009_10_0036</t>
+          <t>CLUB_S2009_10_0060</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -28019,12 +28271,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S2009_10_0054</t>
+          <t>CLUB_S2009_10_0061</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Predators Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -28039,12 +28291,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S2009_10_0057</t>
+          <t>CLUB_S2009_10_0064</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'SHC Maso Brejcha Klatovy' → 'Klatovy' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -28059,12 +28311,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S2009_10_0060</t>
+          <t>CLUB_S2009_10_0070</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -28079,12 +28331,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S2009_10_0061</t>
+          <t>CLUB_S2009_10_0078</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Predators Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Valašský hokejový klub Vsetín' → 'Vsetín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -28099,12 +28351,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S2009_10_0064</t>
+          <t>CLUB_S2009_10_0083</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -28119,12 +28371,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S2009_10_0066</t>
+          <t>CLUB_S2009_10_0086</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'SC Kolín' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -28139,12 +28391,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S2009_10_0070</t>
+          <t>CLUB_S2009_10_0110</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -28159,12 +28411,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S2009_10_0078</t>
+          <t>CLUB_S2009_10_0124</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Valašský hokejový klub Vsetín' → 'Vsetín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -28179,12 +28431,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S2009_10_0083</t>
+          <t>CLUB_S2009_10_0133</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -28199,12 +28451,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S2009_10_0086</t>
+          <t>CLUB_S2009_10_0147</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -28219,12 +28471,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S2009_10_0087</t>
+          <t>CLUB_S2009_10_0148</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -28239,12 +28491,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S2009_10_0110</t>
+          <t>CLUB_S2009_10_0153</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -28259,12 +28511,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S2009_10_0110</t>
+          <t>CLUB_S2009_10_0160</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -28279,12 +28531,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLUB_S2009_10_0118</t>
+          <t>CLUB_S2009_10_0161</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -28299,12 +28551,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLUB_S2009_10_0124</t>
+          <t>CLUB_S2009_10_0170</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
       </c>
     </row>
@@ -28314,17 +28566,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>prev_club_id / identita</t>
+          <t>pyramida (feeds_into)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLUB_S2009_10_0133</t>
+          <t>NODE_S2009_10_0030</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  Skupina A'</t>
         </is>
       </c>
     </row>
@@ -28334,202 +28586,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>prev_club_id / identita</t>
+          <t>pyramida (feeds_into)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLUB_S2009_10_0147</t>
+          <t>NODE_S2009_10_0031</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>CLUB_S2009_10_0148</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>CLUB_S2009_10_0153</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>CLUB_S2009_10_0160</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>CLUB_S2009_10_0161</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>CLUB_S2009_10_0170</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>CLUB_S2009_10_0175</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>CLUB_S2009_10_0192</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>pyramida (feeds_into)</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>NODE_S2009_10_0030</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>top-level kvalifikace bez feeds_into: 'KVAL  Skupina A'</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>pyramida (feeds_into)</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>NODE_S2009_10_0031</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL  Skupina B'</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F35"/>
+  <autoFilter ref="A1:F26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S2009_10_FINAL.xlsx
+++ b/data/S2009_10_FINAL.xlsx
@@ -10912,7 +10912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L92"/>
+  <dimension ref="A1:N92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10976,6 +10976,16 @@
           <t>prev_node_id</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14526,8 +14536,6 @@
         </is>
       </c>
     </row>
-    <row r="79"/>
-    <row r="80"/>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
@@ -14657,7 +14665,6 @@
         </is>
       </c>
     </row>
-    <row r="88"/>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>

--- a/data/S2009_10_FINAL.xlsx
+++ b/data/S2009_10_FINAL.xlsx
@@ -11164,6 +11164,16 @@
           <t>NODE_S2009_10_0001</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0010</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0016</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11178,6 +11188,14 @@
         <is>
           <t>NODE_S2008_09_0004</t>
         </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -11352,6 +11370,16 @@
           <t>NODE_S2009_10_0007</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0010</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0019</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11366,6 +11394,14 @@
         <is>
           <t>NODE_S2008_09_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>horní část ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -11446,6 +11482,16 @@
           <t>NODE_S2009_10_0007</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0011</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0019</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11460,6 +11506,14 @@
         <is>
           <t>NODE_S2008_09_0010</t>
         </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -11493,6 +11547,16 @@
           <t>NODE_S2009_10_0007</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0015</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0014</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11507,6 +11571,14 @@
         <is>
           <t>NODE_S2008_09_0011</t>
         </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -11540,6 +11612,8 @@
           <t>NODE_S2009_10_0007</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11554,6 +11628,14 @@
         <is>
           <t>NODE_S2008_09_0012</t>
         </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -11587,6 +11669,8 @@
           <t>NODE_S2009_10_0007</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11601,6 +11685,14 @@
         <is>
           <t>NODE_S2008_09_0013</t>
         </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -11634,6 +11726,8 @@
           <t>NODE_S2009_10_0007</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11648,6 +11742,14 @@
         <is>
           <t>NODE_S2008_09_0014</t>
         </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -11681,6 +11783,8 @@
           <t>NODE_S2009_10_0007</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11695,6 +11799,14 @@
         <is>
           <t>NODE_S2008_09_0015</t>
         </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -11728,6 +11840,8 @@
           <t>NODE_S2009_10_0001</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11742,6 +11856,14 @@
         <is>
           <t>NODE_S2008_09_0016</t>
         </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -11775,6 +11897,8 @@
           <t>NODE_S2009_10_0007</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11789,6 +11913,14 @@
         <is>
           <t>NODE_S2008_09_0017</t>
         </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -11822,6 +11954,8 @@
           <t>NODE_S2009_10_0007</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11836,6 +11970,14 @@
         <is>
           <t>NODE_S2008_09_0018</t>
         </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>o 9. místo</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -11869,6 +12011,16 @@
           <t>NODE_S2009_10_0007</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0013</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0012</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11883,6 +12035,14 @@
         <is>
           <t>NODE_S2008_09_0019</t>
         </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>poražení ČF</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -12010,6 +12170,16 @@
           <t>NODE_S2009_10_0003</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0023</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0027</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12024,6 +12194,14 @@
         <is>
           <t>NODE_S2008_09_0022</t>
         </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>16 týmů</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -12057,6 +12235,16 @@
           <t>NODE_S2009_10_0003</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0024</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0027</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12071,6 +12259,14 @@
         <is>
           <t>NODE_S2008_09_0023</t>
         </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>střed tabulky ZČ</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -12104,6 +12300,12 @@
           <t>NODE_S2009_10_0003</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0025</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12118,6 +12320,14 @@
         <is>
           <t>NODE_S2008_09_0024</t>
         </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>horní ZČ + postupující z předkola</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -12151,6 +12361,12 @@
           <t>NODE_S2009_10_0003</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0026</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12165,6 +12381,14 @@
         <is>
           <t>NODE_S2008_09_0025</t>
         </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -12198,6 +12422,8 @@
           <t>NODE_S2009_10_0003</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12212,6 +12438,14 @@
         <is>
           <t>NODE_S2008_09_0026</t>
         </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -12245,6 +12479,8 @@
           <t>NODE_S2009_10_0003</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12259,6 +12495,14 @@
         <is>
           <t>NODE_S2008_09_0027</t>
         </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -12737,6 +12981,12 @@
           <t>NODE_S2009_10_0035</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0039</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12751,6 +13001,14 @@
         <is>
           <t>NODE_S2008_09_0039</t>
         </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -12784,6 +13042,12 @@
           <t>NODE_S2009_10_0035</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0040</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12798,6 +13062,14 @@
         <is>
           <t>NODE_S2008_09_0040</t>
         </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="41">
@@ -12831,6 +13103,8 @@
           <t>NODE_S2009_10_0035</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12845,6 +13119,14 @@
         <is>
           <t>NODE_S2008_09_0041</t>
         </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="42">
@@ -12972,6 +13254,8 @@
           <t>NODE_S2009_10_0035</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12986,6 +13270,14 @@
         <is>
           <t>NODE_S2008_09_0044</t>
         </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -13113,6 +13405,12 @@
           <t>NODE_S2009_10_0035</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0038</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13127,6 +13425,14 @@
         <is>
           <t>NODE_S2008_09_0047</t>
         </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>horní část ZČ</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -13207,6 +13513,12 @@
           <t>NODE_S2009_10_0047</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0049</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13221,6 +13533,14 @@
         <is>
           <t>NODE_S2008_09_0049</t>
         </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>12 týmů</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -13254,6 +13574,8 @@
           <t>NODE_S2009_10_0047</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13268,6 +13590,14 @@
         <is>
           <t>NODE_S2008_09_0050</t>
         </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="51">
@@ -13348,6 +13678,12 @@
           <t>NODE_S2009_10_0050</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0052</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13362,6 +13698,14 @@
         <is>
           <t>NODE_S2008_09_0052</t>
         </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>11 týmů</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -13395,6 +13739,8 @@
           <t>NODE_S2009_10_0050</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13409,6 +13755,14 @@
         <is>
           <t>NODE_S2008_09_0053</t>
         </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="54">
@@ -13489,6 +13843,12 @@
           <t>NODE_S2009_10_0053</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0055</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13498,6 +13858,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -13531,6 +13899,8 @@
           <t>NODE_S2009_10_0053</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13540,6 +13910,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="57">
@@ -13667,6 +14045,12 @@
           <t>NODE_S2009_10_0057</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0059</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13681,6 +14065,14 @@
         <is>
           <t>NODE_S2008_09_0058</t>
         </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>5 týmů</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -13714,6 +14106,8 @@
           <t>NODE_S2009_10_0057</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13728,6 +14122,14 @@
         <is>
           <t>NODE_S2008_09_0059</t>
         </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="61">
@@ -13808,6 +14210,12 @@
           <t>NODE_S2009_10_0060</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0064</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13822,6 +14230,14 @@
         <is>
           <t>NODE_S2008_09_0061</t>
         </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>9 týmů</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -13949,6 +14365,8 @@
           <t>NODE_S2009_10_0060</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13958,6 +14376,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="66">
@@ -14038,6 +14464,16 @@
           <t>NODE_S2009_10_0065</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0068</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0067</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14052,6 +14488,14 @@
         <is>
           <t>NODE_S2008_09_0065</t>
         </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -14085,6 +14529,8 @@
           <t>NODE_S2009_10_0065</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14094,6 +14540,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -14127,6 +14581,8 @@
           <t>NODE_S2009_10_0065</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14136,6 +14592,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="70">
@@ -14169,6 +14633,16 @@
           <t>NODE_S2009_10_0065</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0068</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0067</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14183,6 +14657,14 @@
         <is>
           <t>NODE_S2008_09_0065</t>
         </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -14216,6 +14698,8 @@
           <t>NODE_S2009_10_0065</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14225,6 +14709,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="72">
@@ -14305,6 +14797,12 @@
           <t>NODE_S2009_10_0071</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0073</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14319,6 +14817,14 @@
         <is>
           <t>NODE_S2008_09_0073</t>
         </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>10 týmů</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -14352,6 +14858,8 @@
           <t>NODE_S2009_10_0071</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14361,6 +14869,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="75">
@@ -14394,6 +14910,8 @@
           <t>NODE_S2009_10_0071</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14403,6 +14921,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="76">
@@ -14483,6 +15009,12 @@
           <t>NODE_S2009_10_0075</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0077</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14492,6 +15024,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>6 týmů</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -14525,6 +15065,8 @@
           <t>NODE_S2009_10_0075</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14535,7 +15077,17 @@
           <t>complete</t>
         </is>
       </c>
-    </row>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79"/>
+    <row r="80"/>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
@@ -14665,6 +15217,7 @@
         </is>
       </c>
     </row>
+    <row r="88"/>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>

--- a/data/S2009_10_FINAL.xlsx
+++ b/data/S2009_10_FINAL.xlsx
@@ -901,6 +901,11 @@
           <t>HC Eaton Pardubice (C)</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F7" t="n">
         <v>52</v>
       </c>
@@ -11612,8 +11617,6 @@
           <t>NODE_S2009_10_0007</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11669,8 +11672,6 @@
           <t>NODE_S2009_10_0007</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11726,8 +11727,6 @@
           <t>NODE_S2009_10_0007</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11783,8 +11782,6 @@
           <t>NODE_S2009_10_0007</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11840,8 +11837,6 @@
           <t>NODE_S2009_10_0001</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11897,8 +11892,6 @@
           <t>NODE_S2009_10_0007</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11954,8 +11947,6 @@
           <t>NODE_S2009_10_0007</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12305,7 +12296,6 @@
           <t>NODE_S2009_10_0025</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12366,7 +12356,6 @@
           <t>NODE_S2009_10_0026</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12422,8 +12411,6 @@
           <t>NODE_S2009_10_0003</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12479,8 +12466,6 @@
           <t>NODE_S2009_10_0003</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12986,7 +12971,6 @@
           <t>NODE_S2009_10_0039</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13047,7 +13031,6 @@
           <t>NODE_S2009_10_0040</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13103,8 +13086,6 @@
           <t>NODE_S2009_10_0035</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13254,8 +13235,6 @@
           <t>NODE_S2009_10_0035</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13410,7 +13389,6 @@
           <t>NODE_S2009_10_0038</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13518,7 +13496,6 @@
           <t>NODE_S2009_10_0049</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13574,8 +13551,6 @@
           <t>NODE_S2009_10_0047</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13683,7 +13658,6 @@
           <t>NODE_S2009_10_0052</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13739,8 +13713,6 @@
           <t>NODE_S2009_10_0050</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13848,7 +13820,6 @@
           <t>NODE_S2009_10_0055</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13899,8 +13870,6 @@
           <t>NODE_S2009_10_0053</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14050,7 +14019,6 @@
           <t>NODE_S2009_10_0059</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14106,8 +14074,6 @@
           <t>NODE_S2009_10_0057</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14215,7 +14181,6 @@
           <t>NODE_S2009_10_0064</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14365,8 +14330,6 @@
           <t>NODE_S2009_10_0060</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14529,8 +14492,6 @@
           <t>NODE_S2009_10_0065</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14581,8 +14542,6 @@
           <t>NODE_S2009_10_0065</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14698,8 +14657,6 @@
           <t>NODE_S2009_10_0065</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14802,7 +14759,6 @@
           <t>NODE_S2009_10_0073</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14858,8 +14814,6 @@
           <t>NODE_S2009_10_0071</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14910,8 +14864,6 @@
           <t>NODE_S2009_10_0071</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15014,7 +14966,6 @@
           <t>NODE_S2009_10_0077</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15065,8 +15016,6 @@
           <t>NODE_S2009_10_0075</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15086,8 +15035,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79"/>
-    <row r="80"/>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
@@ -15217,7 +15164,6 @@
         </is>
       </c>
     </row>
-    <row r="88"/>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
@@ -28423,7 +28369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28603,6 +28549,18 @@
       <c r="B15" t="inlineStr">
         <is>
           <t>0 oprav kvalifikačních levelů. Sloupec Q (level) aktualizován.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>HC Eaton Pardubice</t>
         </is>
       </c>
     </row>

--- a/data/S2009_10_FINAL.xlsx
+++ b/data/S2009_10_FINAL.xlsx
@@ -15035,6 +15035,8 @@
         <v>5</v>
       </c>
     </row>
+    <row r="79"/>
+    <row r="80"/>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
@@ -15164,6 +15166,7 @@
         </is>
       </c>
     </row>
+    <row r="88"/>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>

--- a/data/S2009_10_FINAL.xlsx
+++ b/data/S2009_10_FINAL.xlsx
@@ -2567,7 +2567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:W24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3838,6 +3838,118 @@
       <c r="V21" t="inlineStr">
         <is>
           <t>SER_S2009_10_0030</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Krajská soutěž</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0078</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>HC Jičín</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Krajská soutěž</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0078</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0194</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00216</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>6</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>HC Varnsdorf</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Krajská soutěž</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0078</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0195</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00217</t>
         </is>
       </c>
     </row>
@@ -5905,7 +6017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W40"/>
+  <dimension ref="A1:W66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -8017,6 +8129,1130 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0079</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>2</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>SB Světlá nad Sázavou</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0079</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0196</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00218</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>7</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>HC Chotěboř</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0079</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0197</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00219</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>5</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Sokol Semechnice</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0079</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0198</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00220</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>6</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Sokol Čestice</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0079</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0199</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00221</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0080</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>SK Žamberk</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0080</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0200</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00222</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Jiskra Králíky</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0080</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0201</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00223</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>3</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Sokol Tisová</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0080</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0202</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00224</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>4</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>HC Dlouhoňovice</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0080</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0203</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00225</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>5</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>TJ Voděrady</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0080</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0204</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00226</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>6</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Sokol Verměřovice</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0080</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0205</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00227</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>7</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Sokol Řetová</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0080</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0206</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00228</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>8</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>HC Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0080</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0207</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00229</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>9</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Sokol Semanín</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0080</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0208</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00230</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>HC Jiskra Skuteč</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0080</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0209</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00231</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ZH Pardubice</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0080</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0210</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00232</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>3</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>SK HC Telmont Chrudim</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0080</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0211</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00233</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>4</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>HC AMAT Pardubice</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0080</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0212</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00234</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>5</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>HC Dynamo Rosice</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0080</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0213</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00235</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>6</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>HC SDH Kostelec u Heř. Městce</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0080</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0214</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00236</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>7</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>HC TPS "B"</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0080</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0215</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00237</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>8</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>HC Zaječice</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0080</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0216</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00238</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>9</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>HC TPS "A"</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0080</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0217</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00239</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>10</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>HC Task Devils Pardubice</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0080</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0218</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00240</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>11</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>HC Wignes Pardubice</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0080</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0219</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00241</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8028,7 +9264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W28"/>
+  <dimension ref="A1:W81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -9560,6 +10796,2359 @@
       <c r="V28" t="inlineStr">
         <is>
           <t>SER_S2009_10_0062</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>HC Blansko</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0220</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00242</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Rájec – Jestřebí</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0221</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00243</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Březina</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0222</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00244</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Sokol Lysice</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0223</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00245</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Černá Hora</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0224</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00246</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>6</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Sokol Sloup</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0225</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00247</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>7</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Adamov</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0226</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00248</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>8</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Letovice</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0227</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00249</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>MÁ Jihlava</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0228</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00250</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Sokol Dlouhá Brtnice</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0229</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00251</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>3</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>HC Chvojkovice – Brod</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0230</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00252</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>4</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>HC Rantířov</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0231</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00253</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>HC Černí kúň</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0232</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00254</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>6</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>HC Velký Beranov</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0233</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00255</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>7</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>HC Amatero</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0234</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00256</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>8</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>HC Janovice</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0235</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00257</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>9</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>HC Kokodáci</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0236</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00258</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>10</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>HC Sokol Kněžice</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0237</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00259</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>11</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>HC Fan Club Dukla Jihlava</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0238</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00260</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Sokol Stařeč</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0239</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00261</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>2</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>HC Pokojovice</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0240</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00262</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>3</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Sokol Okříšky</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0241</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00263</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>4</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>TJ Náměšť nad Oslavou</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0242</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00264</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>5</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>TJ Mohelno /TJ Vladislav</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0243</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00265</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Staré Hvězdy</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0244</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00266</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>2</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>HC Uherský Brod B</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0245</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00267</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>3</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Uherské Hradiště Rangers</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0246</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00268</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>4</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Střelci</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0247</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00269</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>5</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>HC Cyclones</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0248</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00270</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>6</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Moravské kachny</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0249</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00271</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>7</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>MadDogs</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0250</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00272</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>8</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>TJ Bojkovice</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0251</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00273</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>BUM Otrokovice</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0252</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00274</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>2</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>PSVS Napajedla</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0253</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00275</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>3</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>KASMEN Uherský Brod</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0254</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00276</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>4</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Baťovka Zlín</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0255</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00277</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>5</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>WhiteStar Vizovice</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0256</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00278</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>6</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Rudí kohouti Zlín</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0257</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00279</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>7</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>KAS Napajedla</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0258</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00280</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>8</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Lizzaran Šneci Otrokovice</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0259</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00281</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Náměšť nad Oslavou</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0260</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00282</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>2</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>HC Veverská Bitýška</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0261</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00283</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>3</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>SK Mostiště</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0262</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00284</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>4</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>HHK Velké Meziříčí B</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0263</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00285</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>5</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>TJ Řečice</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0264</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00286</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>6</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Spartak Velká Bíteš B</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0265</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00287</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>7</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>HC Sokol Křižanov</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0266</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00288</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>8</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>HC Nedvědice B</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0267</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00289</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>9</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>TJ Šerkovice</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0268</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00290</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0269</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00291</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>SD-CHO 6:6,4:6</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0270</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00292</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>finále: Dvůr-Týniště 7:2</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0271</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>TR_S2009_10_00293</t>
         </is>
       </c>
     </row>
@@ -10917,7 +14506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N92"/>
+  <dimension ref="A1:N96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15192,6 +18781,124 @@
       <c r="A92" t="inlineStr">
         <is>
           <t>II.liga: Západ/Střed/Východ + 8F/QF/SF/finále.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0078</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Liberecký – Krajská soutěž</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0079</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Pardubický – Krajská liga</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0080</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Pardubický – Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0081</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Jihomoravský – Blansko</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>REG_JHM</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0071</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
         </is>
       </c>
     </row>
@@ -18582,7 +22289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J174"/>
+  <dimension ref="A1:J252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="10" max="10"/>
@@ -25898,6 +29605,2502 @@
       <c r="J174" t="inlineStr">
         <is>
           <t>Tatra Kopřivnice</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0194</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>HC Jičín</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>HC Jičín</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>30LIBE</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0195</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>HC Varnsdorf</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>HC Varnsdorf</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>30LIBE</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0196</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>SB Světlá nad Sázavou</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>SB Světlá nad Sázavou</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0197</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>HC Chotěboř</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>HC Chotěboř</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0198</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Sokol Semechnice</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Sokol Semechnice</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0199</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Sokol Čestice</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Sokol Čestice</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0200</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>SK Žamberk</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>SK Žamberk</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0201</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Jiskra Králíky</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Jiskra Králíky</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0202</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Sokol Tisová</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Sokol Tisová</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0203</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>HC Dlouhoňovice</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>HC Dlouhoňovice</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0204</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>TJ Voděrady</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>TJ Voděrady</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0205</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Sokol Verměřovice</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Sokol Verměřovice</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0206</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Sokol Řetová</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Sokol Řetová</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0207</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>HC Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>HC Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0208</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Sokol Semanín</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Sokol Semanín</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0209</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>HC Jiskra Skuteč</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>HC Jiskra Skuteč</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0210</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>ZH Pardubice</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>ZH Pardubice</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0211</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>SK HC Telmont Chrudim</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>SK HC Telmont Chrudim</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0212</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>HC AMAT Pardubice</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>HC AMAT Pardubice</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0213</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>HC Dynamo Rosice</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>HC Dynamo Rosice</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0214</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>HC SDH Kostelec u Heř. Městce</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>HC SDH Kostelec u Heř. Městce</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0215</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>HC TPS "B"</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>HC TPS "B"</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0216</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>HC Zaječice</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>HC Zaječice</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0217</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>HC TPS "A"</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>HC TPS "A"</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0218</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>HC Task Devils Pardubice</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>HC Task Devils Pardubice</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0219</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>HC Wignes Pardubice</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>HC Wignes Pardubice</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0220</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>HC Blansko</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>HC Blansko</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0221</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Rájec – Jestřebí</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Rájec – Jestřebí</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0222</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Březina</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Březina</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0223</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Sokol Lysice</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Sokol Lysice</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0224</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Černá Hora</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Černá Hora</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0225</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Sokol Sloup</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Sokol Sloup</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0226</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Adamov</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Adamov</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0227</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Letovice</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Letovice</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0228</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>MÁ Jihlava</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>MÁ Jihlava</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0229</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Sokol Dlouhá Brtnice</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Sokol Dlouhá Brtnice</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0230</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>HC Chvojkovice – Brod</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>HC Chvojkovice – Brod</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0231</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>HC Rantířov</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>HC Rantířov</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0232</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>HC Černí kúň</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>HC Černí kúň</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0233</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>HC Velký Beranov</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>HC Velký Beranov</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0234</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>HC Amatero</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>HC Amatero</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0235</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>HC Janovice</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>HC Janovice</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0236</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>HC Kokodáci</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>HC Kokodáci</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0237</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>HC Sokol Kněžice</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>HC Sokol Kněžice</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0238</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>HC Fan Club Dukla Jihlava</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>HC Fan Club Dukla Jihlava</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0239</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Sokol Stařeč</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Sokol Stařeč</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0240</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>HC Pokojovice</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>HC Pokojovice</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0241</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Sokol Okříšky</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Sokol Okříšky</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0242</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>TJ Náměšť nad Oslavou</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>TJ Náměšť nad Oslavou</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0243</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>TJ Mohelno /TJ Vladislav</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>TJ Mohelno /TJ Vladislav</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0244</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Staré Hvězdy</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Staré Hvězdy</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0245</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>HC Uherský Brod B</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>HC Uherský Brod B</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0246</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Uherské Hradiště Rangers</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Uherské Hradiště Rangers</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0247</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Střelci</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Střelci</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0248</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>HC Cyclones</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>HC Cyclones</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0249</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Moravské kachny</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Moravské kachny</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0250</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>MadDogs</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>MadDogs</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0251</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>TJ Bojkovice</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>TJ Bojkovice</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0252</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>BUM Otrokovice</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>BUM Otrokovice</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0253</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>PSVS Napajedla</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>PSVS Napajedla</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0254</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>KASMEN Uherský Brod</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>KASMEN Uherský Brod</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0255</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Baťovka Zlín</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Baťovka Zlín</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0256</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>WhiteStar Vizovice</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>WhiteStar Vizovice</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0257</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Rudí kohouti Zlín</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Rudí kohouti Zlín</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0258</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>KAS Napajedla</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>KAS Napajedla</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0259</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Lizzaran Šneci Otrokovice</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Lizzaran Šneci Otrokovice</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0260</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Náměšť nad Oslavou</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Náměšť nad Oslavou</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0261</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>HC Veverská Bitýška</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>HC Veverská Bitýška</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0262</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>SK Mostiště</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>SK Mostiště</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0263</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>HHK Velké Meziříčí B</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>HHK Velké Meziříčí B</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0264</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>TJ Řečice</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>TJ Řečice</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0265</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Spartak Velká Bíteš B</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Spartak Velká Bíteš B</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0266</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>HC Sokol Křižanov</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>HC Sokol Křižanov</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0267</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>HC Nedvědice B</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>HC Nedvědice B</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0268</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>TJ Šerkovice</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>TJ Šerkovice</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0269</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0270</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>SD-CHO 6:6,4:6</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>SD-CHO 6:6,4:6</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>CLUB_S2009_10_0271</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>finále: Dvůr-Týniště 7:2</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>finále: Dvůr-Týniště 7:2</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
         </is>
       </c>
     </row>

--- a/data/S2009_10_FINAL.xlsx
+++ b/data/S2009_10_FINAL.xlsx
@@ -39,7 +39,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,8 +58,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -81,6 +85,11 @@
         <fgColor rgb="00305496"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0B2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -94,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -105,6 +114,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -18624,8 +18635,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79"/>
-    <row r="80"/>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
@@ -18755,7 +18764,6 @@
         </is>
       </c>
     </row>
-    <row r="88"/>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
@@ -34781,7 +34789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -34838,7 +34846,7 @@
           <t>CLUB_S2009_10_0006</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34858,7 +34866,7 @@
           <t>CLUB_S2009_10_0016</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34878,7 +34886,7 @@
           <t>CLUB_S2009_10_0022</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34898,7 +34906,7 @@
           <t>CLUB_S2009_10_0023</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>TBD: city 'Hockey Club Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34918,7 +34926,7 @@
           <t>CLUB_S2009_10_0036</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34938,7 +34946,7 @@
           <t>CLUB_S2009_10_0054</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
@@ -34958,7 +34966,7 @@
           <t>CLUB_S2009_10_0057</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>TBD: city 'SHC Maso Brejcha Klatovy' → 'Klatovy' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34978,7 +34986,7 @@
           <t>CLUB_S2009_10_0060</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34998,7 +35006,7 @@
           <t>CLUB_S2009_10_0061</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>TBD: city 'Predators Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -35018,7 +35026,7 @@
           <t>CLUB_S2009_10_0064</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -35038,7 +35046,7 @@
           <t>CLUB_S2009_10_0070</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -35058,7 +35066,7 @@
           <t>CLUB_S2009_10_0078</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>TBD: city 'Valašský hokejový klub Vsetín' → 'Vsetín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -35078,7 +35086,7 @@
           <t>CLUB_S2009_10_0083</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -35098,7 +35106,7 @@
           <t>CLUB_S2009_10_0086</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -35118,7 +35126,7 @@
           <t>CLUB_S2009_10_0110</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -35138,7 +35146,7 @@
           <t>CLUB_S2009_10_0124</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -35158,7 +35166,7 @@
           <t>CLUB_S2009_10_0133</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
@@ -35178,7 +35186,7 @@
           <t>CLUB_S2009_10_0147</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
@@ -35198,7 +35206,7 @@
           <t>CLUB_S2009_10_0148</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -35218,7 +35226,7 @@
           <t>CLUB_S2009_10_0153</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -35238,7 +35246,7 @@
           <t>CLUB_S2009_10_0160</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -35258,7 +35266,7 @@
           <t>CLUB_S2009_10_0161</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
@@ -35278,7 +35286,7 @@
           <t>CLUB_S2009_10_0170</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
@@ -35298,7 +35306,7 @@
           <t>NODE_S2009_10_0030</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL  Skupina A'</t>
         </is>
@@ -35318,11 +35326,37 @@
           <t>NODE_S2009_10_0031</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL  Skupina B'</t>
         </is>
       </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Liberecký – Krajská soutěž · NODE_S2009_10_0078</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>máme jen 2 týmy (HC Jičín, HC Varnsdorf), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F26"/>

--- a/data/S2009_10_FINAL.xlsx
+++ b/data/S2009_10_FINAL.xlsx
@@ -103,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -116,6 +116,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -14054,7 +14057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14443,6 +14446,23 @@
         </is>
       </c>
       <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0078</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 2 týmy (HC Jičín, HC Varnsdorf), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -35346,7 +35366,7 @@
           <t>Liberecký – Krajská soutěž · NODE_S2009_10_0078</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>máme jen 2 týmy (HC Jičín, HC Varnsdorf), chybí zbytek týmů a tabulka  [torzo-audit]</t>
         </is>

--- a/data/S2009_10_FINAL.xlsx
+++ b/data/S2009_10_FINAL.xlsx
@@ -16217,7 +16217,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>KVAL  Skupina A</t>
+          <t>KVAL Skupina A</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>KVAL  Skupina B</t>
+          <t>KVAL Skupina B</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -16291,7 +16291,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>30_Praha L40</t>
+          <t>Praha, 4. úroveň</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -16338,7 +16338,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>30_Praha L50</t>
+          <t>Praha, 5. úroveň</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -16380,7 +16380,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>30_Praha L50</t>
+          <t>Praha, 5. úroveň</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -17041,7 +17041,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>30_Středočeský L40</t>
+          <t>Středočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -17088,7 +17088,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 základní část</t>
+          <t>Středočeský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -17148,7 +17148,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 Finále</t>
+          <t>Středočeský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -17203,7 +17203,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40</t>
+          <t>Jihočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -17250,7 +17250,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 základní část</t>
+          <t>Jihočeský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -17310,7 +17310,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 Finále</t>
+          <t>Jihočeský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -17365,7 +17365,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40</t>
+          <t>Plzeňský, 4. úroveň</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -17412,7 +17412,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40 základní část</t>
+          <t>Plzeňský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -17467,7 +17467,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40 Finále</t>
+          <t>Plzeňský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -17517,7 +17517,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>30_Ústecký-Karlovarský L40</t>
+          <t>Ústecký-Karlovarský, 4. úroveň</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -17564,7 +17564,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>30_Liberecký L40</t>
+          <t>Liberecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -17611,7 +17611,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>30_Liberecký L40 základní část</t>
+          <t>Liberecký, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -17671,7 +17671,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>30_Liberecký L40 Finále</t>
+          <t>Liberecký, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -17726,7 +17726,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>30_Hradecký L40</t>
+          <t>Hradecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -17773,7 +17773,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>30_Hradecký L40 základní část</t>
+          <t>Hradecký, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -17833,7 +17833,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>30_Hradecký L40 skupina A</t>
+          <t>Hradecký, 4. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -17880,7 +17880,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>30_Hradecký L40 skupina B</t>
+          <t>Hradecký, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -17927,7 +17927,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>30_Hradecký L40 Finále</t>
+          <t>Hradecký, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -17977,7 +17977,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>30_Pardubický L40</t>
+          <t>Pardubický, 4. úroveň</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -18024,7 +18024,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>30_Pardubický L40 základní část</t>
+          <t>Pardubický, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>30_Pardubický L40 O udržení</t>
+          <t>Pardubický, 4. úroveň O udržení</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -18139,7 +18139,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>30_Pardubický L40 Finále</t>
+          <t>Pardubický, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -18189,7 +18189,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>30_Pardubický L40 základní část</t>
+          <t>Pardubický, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -18254,7 +18254,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>30_Pardubický L40 Finále</t>
+          <t>Pardubický, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -18304,7 +18304,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40</t>
+          <t>Jihomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -18351,7 +18351,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 základní část</t>
+          <t>Jihomoravský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -18411,7 +18411,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 Finále</t>
+          <t>Jihomoravský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -18461,7 +18461,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 Finále</t>
+          <t>Jihomoravský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -18511,7 +18511,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40</t>
+          <t>Severomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -18558,7 +18558,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40 základní část</t>
+          <t>Severomoravský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -18613,7 +18613,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40 Finále</t>
+          <t>Severomoravský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -18655,6 +18655,8 @@
         <v>5</v>
       </c>
     </row>
+    <row r="79"/>
+    <row r="80"/>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
@@ -18687,7 +18689,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
+          <t>I.ČNHL (12 CZ) + SNHL (12 Slovensko)</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -18784,6 +18786,7 @@
         </is>
       </c>
     </row>
+    <row r="88"/>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>

--- a/data/S2009_10_FINAL.xlsx
+++ b/data/S2009_10_FINAL.xlsx
@@ -817,7 +817,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -6557,7 +6557,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -6713,7 +6713,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -18655,8 +18655,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79"/>
-    <row r="80"/>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
@@ -18786,7 +18784,6 @@
         </is>
       </c>
     </row>
-    <row r="88"/>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
@@ -32438,7 +32435,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -32516,7 +32513,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -32594,7 +32591,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -32672,7 +32669,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -32750,7 +32747,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -32828,7 +32825,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -32906,7 +32903,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -32984,7 +32981,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -33067,7 +33064,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>slouceni</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -33145,7 +33142,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -33223,7 +33220,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -33301,7 +33298,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -33379,7 +33376,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -33457,7 +33454,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -33540,7 +33537,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -33618,7 +33615,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>sestup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
